--- a/artfynd/A 12353-2022 artfynd.xlsx
+++ b/artfynd/A 12353-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12353-2022 artfynd.xlsx
+++ b/artfynd/A 12353-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113001303</v>
+        <v>113001307</v>
       </c>
       <c r="B2" t="n">
-        <v>96255</v>
+        <v>102435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,23 +687,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>222075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Mörk dunört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Epilobium obscurum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,7 +721,7 @@
         <v>6447765</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -778,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113001307</v>
+        <v>113001298</v>
       </c>
       <c r="B3" t="n">
-        <v>102435</v>
+        <v>102947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222075</v>
+        <v>220461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk dunört</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epilobium obscurum</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>With.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,7 +828,7 @@
         <v>6447765</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113001298</v>
+        <v>113001300</v>
       </c>
       <c r="B4" t="n">
-        <v>102947</v>
+        <v>94092</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220461</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>With.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -992,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113001300</v>
+        <v>113001299</v>
       </c>
       <c r="B5" t="n">
-        <v>94092</v>
+        <v>93347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2383</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1099,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113001299</v>
+        <v>113001301</v>
       </c>
       <c r="B6" t="n">
-        <v>93347</v>
+        <v>94893</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2383</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1145,7 +1149,7 @@
         <v>6447765</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,113 +1207,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>113001301</v>
-      </c>
-      <c r="B7" t="n">
-        <v>94893</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2590</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Kornknutmossa</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Odontoschisma denudatum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Sumpskog Södra Helliden, sydost om Tidaholm, Vg</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>439673</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6447765</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Tidaholm</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Agnetorp</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering SUNDH MILJÖ AB</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Lennart Sundh</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Lennart Sundh</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12353-2022 artfynd.xlsx
+++ b/artfynd/A 12353-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113001307</v>
+        <v>113001303</v>
       </c>
       <c r="B2" t="n">
-        <v>102435</v>
+        <v>96255</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,27 +687,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222075</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk dunört</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epilobium obscurum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,7 +717,7 @@
         <v>6447765</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113001298</v>
+        <v>113001307</v>
       </c>
       <c r="B3" t="n">
-        <v>102947</v>
+        <v>102435</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +790,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220461</v>
+        <v>222075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Mörk dunört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Epilobium obscurum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>With.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,7 +824,7 @@
         <v>6447765</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113001300</v>
+        <v>113001298</v>
       </c>
       <c r="B4" t="n">
-        <v>94092</v>
+        <v>102947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>With.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113001299</v>
+        <v>113001300</v>
       </c>
       <c r="B5" t="n">
-        <v>93347</v>
+        <v>94092</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1008,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2383</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1103,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113001301</v>
+        <v>113001299</v>
       </c>
       <c r="B6" t="n">
-        <v>94893</v>
+        <v>93347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>2383</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,7 +1145,7 @@
         <v>6447765</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,6 +1203,113 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113001301</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94893</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sumpskog Södra Helliden, sydost om Tidaholm, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>439673</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6447765</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Agnetorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering SUNDH MILJÖ AB</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12353-2022 artfynd.xlsx
+++ b/artfynd/A 12353-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113001303</v>
+        <v>113001300</v>
       </c>
       <c r="B2" t="n">
-        <v>96255</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439673</v>
+        <v>439672</v>
       </c>
       <c r="R2" t="n">
         <v>6447765</v>
@@ -778,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113001307</v>
+        <v>113001299</v>
       </c>
       <c r="B3" t="n">
-        <v>102435</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222075</v>
+        <v>2383</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk dunört</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epilobium obscurum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439673</v>
+        <v>439672</v>
       </c>
       <c r="R3" t="n">
         <v>6447765</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113001298</v>
+        <v>113001301</v>
       </c>
       <c r="B4" t="n">
-        <v>102947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220461</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>With.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,13 +914,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439673</v>
+        <v>439672</v>
       </c>
       <c r="R4" t="n">
         <v>6447765</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113001300</v>
+        <v>113001270</v>
       </c>
       <c r="B5" t="n">
-        <v>94092</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1008,37 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sumpskog Södra Helliden, sydost om Tidaholm, Vg</t>
+          <t>Skog Södra Helliden, sydost om Tidaholm, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439673</v>
+        <v>439667</v>
       </c>
       <c r="R5" t="n">
-        <v>6447765</v>
+        <v>6447866</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113001299</v>
+        <v>113001298</v>
       </c>
       <c r="B6" t="n">
-        <v>93347</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2383</v>
+        <v>220461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>With.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,7 +1118,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439673</v>
+        <v>439672</v>
       </c>
       <c r="R6" t="n">
         <v>6447765</v>
@@ -1206,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113001301</v>
+        <v>113001303</v>
       </c>
       <c r="B7" t="n">
-        <v>94893</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,23 +1196,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>221944</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1246,13 +1216,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439673</v>
+        <v>439672</v>
       </c>
       <c r="R7" t="n">
         <v>6447765</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,6 +1280,210 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113001288</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sumpskog Södra Helliden, sydost om Tidaholm, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>439619</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6447798</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Agnetorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering SUNDH MILJÖ AB</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113001307</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104283</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222075</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk dunört</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Epilobium obscurum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sumpskog Södra Helliden, sydost om Tidaholm, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>439672</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6447765</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Agnetorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering SUNDH MILJÖ AB</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12353-2022 artfynd.xlsx
+++ b/artfynd/A 12353-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113001300</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113001299</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113001301</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113001270</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113001298</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113001303</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113001288</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,8 +1524,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113001307</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>